--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -792,12 +792,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Josefin Stagnell</t>
+          <t>Josefin Hagernäs</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Josefin Stagnell</t>
+          <t>Josefin Hagernäs</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128287732</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97350</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>619581</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6568338</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128287732</v>
       </c>
       <c r="B3" t="n">
-        <v>97350</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128287732</v>
       </c>
       <c r="B3" t="n">
-        <v>97358</v>
+        <v>97451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128287732</v>
       </c>
       <c r="B3" t="n">
-        <v>97451</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128287732</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128287732</v>
       </c>
       <c r="B3" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128287732</v>
       </c>
       <c r="B3" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128287732</v>
       </c>
       <c r="B3" t="n">
-        <v>97493</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118470718</v>
+        <v>125453888</v>
       </c>
       <c r="B2" t="n">
-        <v>56186</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålpussen, Srm</t>
+          <t>Lundby skog, Lundby skog, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619494</v>
+        <v>619264</v>
       </c>
       <c r="R2" t="n">
-        <v>6568288</v>
+        <v>6568144</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,61 +775,90 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Josefin Hagernäs</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Josefin Hagernäs</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128287732</v>
+        <v>120700522</v>
       </c>
       <c r="B3" t="n">
-        <v>97506</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ålpussen, Ålpussen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619581</v>
+        <v>619444</v>
       </c>
       <c r="R3" t="n">
-        <v>6568338</v>
+        <v>6568281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,22 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,6 +911,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,6 +929,848 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120700695</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>619429</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6568250</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120701492</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>619505</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6568345</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125787370</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>619392</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6568185</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>02:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>02:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118470718</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>619494</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568288</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23:57</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>23:57</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Josefin Hagernäs</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Josefin Hagernäs</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125454581</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>619270</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568139</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125455369</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lundby skog, Lundby skog, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>619299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568135</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128287732</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ålpussen, Ålpussen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>619581</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568338</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6570-2023 artfynd.xlsx
+++ b/artfynd/A 6570-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125453888</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,6 +939,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120700522</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120700695</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1171,6 +1191,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120701492</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1308,6 +1333,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125787370</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1432,6 +1462,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118470718</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1548,6 +1583,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125454581</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1664,6 +1704,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125455369</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1771,8 +1816,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128287732</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>